--- a/Assets/Excel/Tree.xlsx
+++ b/Assets/Excel/Tree.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1BFE8F-1E78-49C5-B2FC-C72BB609566E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E107A30B-C752-4C41-97D4-FE66C06BAE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4275" yWindow="1665" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment" sheetId="1" r:id="rId1"/>
@@ -79,10 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>升级时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>LvUpCost</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -108,6 +104,10 @@
   </si>
   <si>
     <t>Rare6Weight</t>
+  </si>
+  <si>
+    <t>升级时间（秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -492,7 +492,7 @@
         <v>11</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
@@ -539,28 +539,28 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="I3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -592,7 +592,7 @@
         <v>1000</v>
       </c>
       <c r="J4" s="2">
-        <v>3600</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -624,7 +624,7 @@
         <v>2000</v>
       </c>
       <c r="J5" s="2">
-        <v>7200</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -656,7 +656,7 @@
         <v>3000</v>
       </c>
       <c r="J6" s="2">
-        <v>10800</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -688,7 +688,7 @@
         <v>4000</v>
       </c>
       <c r="J7" s="2">
-        <v>14400</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -720,7 +720,7 @@
         <v>5000</v>
       </c>
       <c r="J8" s="2">
-        <v>18000</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -752,7 +752,7 @@
         <v>6000</v>
       </c>
       <c r="J9" s="2">
-        <v>21600</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -784,7 +784,7 @@
         <v>7000</v>
       </c>
       <c r="J10" s="2">
-        <v>25200</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -816,7 +816,7 @@
         <v>8000</v>
       </c>
       <c r="J11" s="2">
-        <v>28800</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -848,7 +848,7 @@
         <v>9000</v>
       </c>
       <c r="J12" s="2">
-        <v>32400</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
@@ -880,7 +880,7 @@
         <v>10000</v>
       </c>
       <c r="J13" s="2">
-        <v>36000</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -912,7 +912,7 @@
         <v>11000</v>
       </c>
       <c r="J14" s="2">
-        <v>39600</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -944,7 +944,7 @@
         <v>12000</v>
       </c>
       <c r="J15" s="2">
-        <v>43200</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -976,7 +976,7 @@
         <v>13000</v>
       </c>
       <c r="J16" s="2">
-        <v>46800</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -1008,7 +1008,7 @@
         <v>14000</v>
       </c>
       <c r="J17" s="2">
-        <v>50400</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -1040,7 +1040,7 @@
         <v>15000</v>
       </c>
       <c r="J18" s="2">
-        <v>54000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -1072,7 +1072,7 @@
         <v>16000</v>
       </c>
       <c r="J19" s="2">
-        <v>57600</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -1104,7 +1104,7 @@
         <v>17000</v>
       </c>
       <c r="J20" s="2">
-        <v>61200</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -1136,7 +1136,7 @@
         <v>18000</v>
       </c>
       <c r="J21" s="2">
-        <v>64800</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -1168,7 +1168,7 @@
         <v>19000</v>
       </c>
       <c r="J22" s="2">
-        <v>68400</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -1200,7 +1200,7 @@
         <v>20000</v>
       </c>
       <c r="J23" s="2">
-        <v>72000</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -1232,7 +1232,7 @@
         <v>21000</v>
       </c>
       <c r="J24" s="2">
-        <v>75600</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -1264,7 +1264,7 @@
         <v>22000</v>
       </c>
       <c r="J25" s="2">
-        <v>79200</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -1296,7 +1296,7 @@
         <v>23000</v>
       </c>
       <c r="J26" s="2">
-        <v>82800</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -1328,7 +1328,7 @@
         <v>24000</v>
       </c>
       <c r="J27" s="2">
-        <v>86400</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -1360,7 +1360,7 @@
         <v>25000</v>
       </c>
       <c r="J28" s="2">
-        <v>90000</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -1392,7 +1392,7 @@
         <v>26000</v>
       </c>
       <c r="J29" s="2">
-        <v>93600</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -1424,7 +1424,7 @@
         <v>27000</v>
       </c>
       <c r="J30" s="2">
-        <v>97200</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
@@ -1456,7 +1456,7 @@
         <v>28000</v>
       </c>
       <c r="J31" s="2">
-        <v>100800</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
@@ -1488,7 +1488,7 @@
         <v>29000</v>
       </c>
       <c r="J32" s="2">
-        <v>104400</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
@@ -1520,7 +1520,7 @@
         <v>30000</v>
       </c>
       <c r="J33" s="2">
-        <v>108000</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -1552,7 +1552,7 @@
         <v>31000</v>
       </c>
       <c r="J34" s="2">
-        <v>111600</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
@@ -1584,7 +1584,7 @@
         <v>32000</v>
       </c>
       <c r="J35" s="2">
-        <v>115200</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -1616,7 +1616,7 @@
         <v>33000</v>
       </c>
       <c r="J36" s="2">
-        <v>118800</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -1648,7 +1648,7 @@
         <v>34000</v>
       </c>
       <c r="J37" s="2">
-        <v>122400</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
@@ -1680,7 +1680,7 @@
         <v>35000</v>
       </c>
       <c r="J38" s="2">
-        <v>126000</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -1712,7 +1712,7 @@
         <v>36000</v>
       </c>
       <c r="J39" s="2">
-        <v>129600</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/Tree.xlsx
+++ b/Assets/Excel/Tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E107A30B-C752-4C41-97D4-FE66C06BAE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A1AFFF-60FF-423F-BB2A-48BDA701DE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>Int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -108,13 +108,54 @@
   <si>
     <t>升级时间（秒）</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品质1概率</t>
+  </si>
+  <si>
+    <t>品质2概率</t>
+  </si>
+  <si>
+    <t>品质3概率</t>
+  </si>
+  <si>
+    <t>品质4概率</t>
+  </si>
+  <si>
+    <t>品质5概率</t>
+  </si>
+  <si>
+    <t>品质6概率</t>
+  </si>
+  <si>
+    <t>Float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare1Rate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare2Rate</t>
+  </si>
+  <si>
+    <t>Rare3Rate</t>
+  </si>
+  <si>
+    <t>Rare4Rate</t>
+  </si>
+  <si>
+    <t>Rare5Rate</t>
+  </si>
+  <si>
+    <t>Rare6Rate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,13 +179,32 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -156,10 +216,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -170,8 +233,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -450,56 +523,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="12.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="3" max="14" width="12.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -525,13 +613,31 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -557,13 +663,31 @@
         <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -571,13 +695,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="2">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D4" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -588,14 +712,38 @@
       <c r="H4" s="2">
         <v>0</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="6">
+        <f>C4/SUM($C4:$H4)</f>
+        <v>0.75</v>
+      </c>
+      <c r="J4" s="6">
+        <f t="shared" ref="J4:N4" si="0">D4/SUM($C4:$H4)</f>
+        <v>0.1875</v>
+      </c>
+      <c r="K4" s="6">
+        <f t="shared" si="0"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="L4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
         <v>1000</v>
       </c>
-      <c r="J4" s="2">
+      <c r="P4" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -603,13 +751,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="2">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
@@ -620,14 +768,38 @@
       <c r="H5" s="2">
         <v>0</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="6">
+        <f t="shared" ref="I5:I39" si="1">C5/SUM($C5:$H5)</f>
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="J5" s="6">
+        <f t="shared" ref="J5:J39" si="2">D5/SUM($C5:$H5)</f>
+        <v>0.2</v>
+      </c>
+      <c r="K5" s="6">
+        <f t="shared" ref="K5:K39" si="3">E5/SUM($C5:$H5)</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="L5" s="6">
+        <f t="shared" ref="L5:L39" si="4">F5/SUM($C5:$H5)</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="6">
+        <f t="shared" ref="M5:M39" si="5">G5/SUM($C5:$H5)</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="6">
+        <f t="shared" ref="N5:N39" si="6">H5/SUM($C5:$H5)</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="2">
         <v>2000</v>
       </c>
-      <c r="J5" s="2">
+      <c r="P5" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -635,13 +807,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="2">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -652,14 +824,38 @@
       <c r="H6" s="2">
         <v>0</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="6">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="J6" s="6">
+        <f t="shared" si="2"/>
+        <v>0.21249999999999999</v>
+      </c>
+      <c r="K6" s="6">
+        <f t="shared" si="3"/>
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="L6" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N6" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O6" s="2">
         <v>3000</v>
       </c>
-      <c r="J6" s="2">
+      <c r="P6" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -667,13 +863,13 @@
         <v>4</v>
       </c>
       <c r="C7" s="2">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="D7" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -684,14 +880,38 @@
       <c r="H7" s="2">
         <v>0</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="6">
+        <f t="shared" si="1"/>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="J7" s="6">
+        <f t="shared" si="2"/>
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="K7" s="6">
+        <f t="shared" si="3"/>
+        <v>0.1</v>
+      </c>
+      <c r="L7" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N7" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
         <v>4000</v>
       </c>
-      <c r="J7" s="2">
+      <c r="P7" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -699,13 +919,13 @@
         <v>5</v>
       </c>
       <c r="C8" s="2">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="D8" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E8" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -716,14 +936,38 @@
       <c r="H8" s="2">
         <v>0</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="6">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="J8" s="6">
+        <f t="shared" si="2"/>
+        <v>0.23749999999999999</v>
+      </c>
+      <c r="K8" s="6">
+        <f t="shared" si="3"/>
+        <v>0.1125</v>
+      </c>
+      <c r="L8" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O8" s="2">
         <v>5000</v>
       </c>
-      <c r="J8" s="2">
+      <c r="P8" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -731,10 +975,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="2">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D9" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2">
         <v>10</v>
@@ -748,14 +992,38 @@
       <c r="H9" s="2">
         <v>0</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="6">
+        <f t="shared" si="1"/>
+        <v>0.625</v>
+      </c>
+      <c r="J9" s="6">
+        <f t="shared" si="2"/>
+        <v>0.25</v>
+      </c>
+      <c r="K9" s="6">
+        <f t="shared" si="3"/>
+        <v>0.125</v>
+      </c>
+      <c r="L9" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="2">
         <v>6000</v>
       </c>
-      <c r="J9" s="2">
+      <c r="P9" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -763,13 +1031,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="2">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D10" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
@@ -780,14 +1048,38 @@
       <c r="H10" s="2">
         <v>0</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="6">
+        <f t="shared" si="1"/>
+        <v>0.6</v>
+      </c>
+      <c r="J10" s="6">
+        <f t="shared" si="2"/>
+        <v>0.26250000000000001</v>
+      </c>
+      <c r="K10" s="6">
+        <f t="shared" si="3"/>
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="L10" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="2">
         <v>7000</v>
       </c>
-      <c r="J10" s="2">
+      <c r="P10" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -795,13 +1087,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="2">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="D11" s="2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E11" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
@@ -812,14 +1104,38 @@
       <c r="H11" s="2">
         <v>0</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="6">
+        <f t="shared" si="1"/>
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="J11" s="6">
+        <f t="shared" si="2"/>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="K11" s="6">
+        <f t="shared" si="3"/>
+        <v>0.15</v>
+      </c>
+      <c r="L11" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="2">
         <v>8000</v>
       </c>
-      <c r="J11" s="2">
+      <c r="P11" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -827,13 +1143,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="2">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D12" s="2">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
@@ -844,14 +1160,38 @@
       <c r="H12" s="2">
         <v>0</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="6">
+        <f t="shared" si="1"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J12" s="6">
+        <f t="shared" si="2"/>
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="K12" s="6">
+        <f t="shared" si="3"/>
+        <v>0.16250000000000001</v>
+      </c>
+      <c r="L12" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N12" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="2">
         <v>9000</v>
       </c>
-      <c r="J12" s="2">
+      <c r="P12" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -859,13 +1199,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="2">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
@@ -876,14 +1216,38 @@
       <c r="H13" s="2">
         <v>0</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="6">
+        <f t="shared" si="1"/>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="J13" s="6">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+      <c r="K13" s="6">
+        <f t="shared" si="3"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="L13" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N13" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="2">
         <v>10000</v>
       </c>
-      <c r="J13" s="2">
+      <c r="P13" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -891,13 +1255,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D14" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -908,14 +1272,38 @@
       <c r="H14" s="2">
         <v>0</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="J14" s="6">
+        <f t="shared" si="2"/>
+        <v>0.3125</v>
+      </c>
+      <c r="K14" s="6">
+        <f t="shared" si="3"/>
+        <v>0.1875</v>
+      </c>
+      <c r="L14" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N14" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="2">
         <v>11000</v>
       </c>
-      <c r="J14" s="2">
+      <c r="P14" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -923,13 +1311,13 @@
         <v>12</v>
       </c>
       <c r="C15" s="2">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="D15" s="2">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E15" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
@@ -940,14 +1328,38 @@
       <c r="H15" s="2">
         <v>0</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="6">
+        <f t="shared" si="1"/>
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="J15" s="6">
+        <f t="shared" si="2"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="K15" s="6">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="L15" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N15" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="2">
         <v>12000</v>
       </c>
-      <c r="J15" s="2">
+      <c r="P15" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -955,16 +1367,16 @@
         <v>13</v>
       </c>
       <c r="C16" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F16" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
@@ -972,14 +1384,38 @@
       <c r="H16" s="2">
         <v>0</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="6">
+        <f t="shared" si="2"/>
+        <v>0.45</v>
+      </c>
+      <c r="K16" s="6">
+        <f t="shared" si="3"/>
+        <v>0.35</v>
+      </c>
+      <c r="L16" s="6">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="M16" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="2">
         <v>13000</v>
       </c>
-      <c r="J16" s="2">
+      <c r="P16" s="2">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -987,16 +1423,16 @@
         <v>14</v>
       </c>
       <c r="C17" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F17" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
@@ -1004,14 +1440,38 @@
       <c r="H17" s="2">
         <v>0</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="6">
+        <f t="shared" si="2"/>
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="K17" s="6">
+        <f t="shared" si="3"/>
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="L17" s="6">
+        <f t="shared" si="4"/>
+        <v>0.21249999999999999</v>
+      </c>
+      <c r="M17" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="2">
         <v>14000</v>
       </c>
-      <c r="J17" s="2">
+      <c r="P17" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -1019,16 +1479,16 @@
         <v>15</v>
       </c>
       <c r="C18" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F18" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
@@ -1036,14 +1496,38 @@
       <c r="H18" s="2">
         <v>0</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="6">
+        <f t="shared" si="2"/>
+        <v>0.4</v>
+      </c>
+      <c r="K18" s="6">
+        <f t="shared" si="3"/>
+        <v>0.375</v>
+      </c>
+      <c r="L18" s="6">
+        <f t="shared" si="4"/>
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="M18" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="2">
         <v>15000</v>
       </c>
-      <c r="J18" s="2">
+      <c r="P18" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -1051,16 +1535,16 @@
         <v>16</v>
       </c>
       <c r="C19" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E19" s="2">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F19" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
@@ -1068,14 +1552,38 @@
       <c r="H19" s="2">
         <v>0</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="6">
+        <f t="shared" si="2"/>
+        <v>0.375</v>
+      </c>
+      <c r="K19" s="6">
+        <f t="shared" si="3"/>
+        <v>0.38750000000000001</v>
+      </c>
+      <c r="L19" s="6">
+        <f t="shared" si="4"/>
+        <v>0.23749999999999999</v>
+      </c>
+      <c r="M19" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="2">
         <v>16000</v>
       </c>
-      <c r="J19" s="2">
+      <c r="P19" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -1083,16 +1591,16 @@
         <v>17</v>
       </c>
       <c r="C20" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E20" s="2">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F20" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
@@ -1100,14 +1608,38 @@
       <c r="H20" s="2">
         <v>0</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="6">
+        <f t="shared" si="2"/>
+        <v>0.35</v>
+      </c>
+      <c r="K20" s="6">
+        <f t="shared" si="3"/>
+        <v>0.4</v>
+      </c>
+      <c r="L20" s="6">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="M20" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="2">
         <v>17000</v>
       </c>
-      <c r="J20" s="2">
+      <c r="P20" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -1115,16 +1647,16 @@
         <v>18</v>
       </c>
       <c r="C21" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E21" s="2">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
@@ -1132,14 +1664,38 @@
       <c r="H21" s="2">
         <v>0</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="6">
+        <f t="shared" si="2"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="K21" s="6">
+        <f t="shared" si="3"/>
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="L21" s="6">
+        <f t="shared" si="4"/>
+        <v>0.26250000000000001</v>
+      </c>
+      <c r="M21" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="2">
         <v>18000</v>
       </c>
-      <c r="J21" s="2">
+      <c r="P21" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -1147,16 +1703,16 @@
         <v>19</v>
       </c>
       <c r="C22" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E22" s="2">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
@@ -1164,14 +1720,38 @@
       <c r="H22" s="2">
         <v>0</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="6">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+      <c r="K22" s="6">
+        <f t="shared" si="3"/>
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="L22" s="6">
+        <f t="shared" si="4"/>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="M22" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="2">
         <v>19000</v>
       </c>
-      <c r="J22" s="2">
+      <c r="P22" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -1179,16 +1759,16 @@
         <v>20</v>
       </c>
       <c r="C23" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E23" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
@@ -1196,14 +1776,38 @@
       <c r="H23" s="2">
         <v>0</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="6">
+        <f t="shared" si="2"/>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="K23" s="6">
+        <f t="shared" si="3"/>
+        <v>0.4375</v>
+      </c>
+      <c r="L23" s="6">
+        <f t="shared" si="4"/>
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="M23" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="2">
         <v>20000</v>
       </c>
-      <c r="J23" s="2">
+      <c r="P23" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -1211,16 +1815,16 @@
         <v>21</v>
       </c>
       <c r="C24" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D24" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
@@ -1228,14 +1832,38 @@
       <c r="H24" s="2">
         <v>0</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="6">
+        <f t="shared" si="2"/>
+        <v>0.25</v>
+      </c>
+      <c r="K24" s="6">
+        <f t="shared" si="3"/>
+        <v>0.45</v>
+      </c>
+      <c r="L24" s="6">
+        <f t="shared" si="4"/>
+        <v>0.3</v>
+      </c>
+      <c r="M24" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="2">
         <v>21000</v>
       </c>
-      <c r="J24" s="2">
+      <c r="P24" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -1243,16 +1871,16 @@
         <v>22</v>
       </c>
       <c r="C25" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D25" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E25" s="2">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
@@ -1260,14 +1888,38 @@
       <c r="H25" s="2">
         <v>0</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="6">
+        <f t="shared" si="2"/>
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="K25" s="6">
+        <f t="shared" si="3"/>
+        <v>0.46250000000000002</v>
+      </c>
+      <c r="L25" s="6">
+        <f t="shared" si="4"/>
+        <v>0.3125</v>
+      </c>
+      <c r="M25" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="2">
         <v>22000</v>
       </c>
-      <c r="J25" s="2">
+      <c r="P25" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -1275,16 +1927,16 @@
         <v>23</v>
       </c>
       <c r="C26" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D26" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E26" s="2">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
@@ -1292,14 +1944,38 @@
       <c r="H26" s="2">
         <v>0</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="6">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+      <c r="K26" s="6">
+        <f t="shared" si="3"/>
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="L26" s="6">
+        <f t="shared" si="4"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M26" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="2">
         <v>23000</v>
       </c>
-      <c r="J26" s="2">
+      <c r="P26" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -1307,16 +1983,16 @@
         <v>24</v>
       </c>
       <c r="C27" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D27" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E27" s="2">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
@@ -1324,14 +2000,38 @@
       <c r="H27" s="2">
         <v>0</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="6">
+        <f t="shared" si="2"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="K27" s="6">
+        <f t="shared" si="3"/>
+        <v>0.48749999999999999</v>
+      </c>
+      <c r="L27" s="6">
+        <f t="shared" si="4"/>
+        <v>0.33750000000000002</v>
+      </c>
+      <c r="M27" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="2">
         <v>24000</v>
       </c>
-      <c r="J27" s="2">
+      <c r="P27" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -1339,31 +2039,55 @@
         <v>25</v>
       </c>
       <c r="C28" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D28" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E28" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G28" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H28" s="2">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2">
+        <v>12</v>
+      </c>
+      <c r="I28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="M28" s="6">
+        <f t="shared" si="5"/>
+        <v>0.35</v>
+      </c>
+      <c r="N28" s="6">
+        <f t="shared" si="6"/>
+        <v>0.15</v>
+      </c>
+      <c r="O28" s="2">
         <v>25000</v>
       </c>
-      <c r="J28" s="2">
+      <c r="P28" s="2">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -1371,31 +2095,55 @@
         <v>26</v>
       </c>
       <c r="C29" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D29" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G29" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H29" s="2">
-        <v>0</v>
-      </c>
-      <c r="I29" s="2">
+        <v>12</v>
+      </c>
+      <c r="I29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="6">
+        <f t="shared" si="4"/>
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="M29" s="6">
+        <f t="shared" si="5"/>
+        <v>0.375</v>
+      </c>
+      <c r="N29" s="6">
+        <f t="shared" si="6"/>
+        <v>0.15</v>
+      </c>
+      <c r="O29" s="2">
         <v>26000</v>
       </c>
-      <c r="J29" s="2">
+      <c r="P29" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -1403,31 +2151,55 @@
         <v>27</v>
       </c>
       <c r="C30" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D30" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E30" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G30" s="2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H30" s="2">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2">
+        <v>12</v>
+      </c>
+      <c r="I30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="6">
+        <f t="shared" si="4"/>
+        <v>0.45</v>
+      </c>
+      <c r="M30" s="6">
+        <f t="shared" si="5"/>
+        <v>0.4</v>
+      </c>
+      <c r="N30" s="6">
+        <f t="shared" si="6"/>
+        <v>0.15</v>
+      </c>
+      <c r="O30" s="2">
         <v>27000</v>
       </c>
-      <c r="J30" s="2">
+      <c r="P30" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -1435,31 +2207,55 @@
         <v>28</v>
       </c>
       <c r="C31" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D31" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G31" s="2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H31" s="2">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2">
+        <v>12</v>
+      </c>
+      <c r="I31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="6">
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="M31" s="6">
+        <f t="shared" si="5"/>
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="N31" s="6">
+        <f t="shared" si="6"/>
+        <v>0.15</v>
+      </c>
+      <c r="O31" s="2">
         <v>28000</v>
       </c>
-      <c r="J31" s="2">
+      <c r="P31" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -1467,31 +2263,55 @@
         <v>29</v>
       </c>
       <c r="C32" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D32" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E32" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G32" s="2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H32" s="2">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
+        <v>12</v>
+      </c>
+      <c r="I32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="6">
+        <f t="shared" si="4"/>
+        <v>0.4</v>
+      </c>
+      <c r="M32" s="6">
+        <f t="shared" si="5"/>
+        <v>0.45</v>
+      </c>
+      <c r="N32" s="6">
+        <f t="shared" si="6"/>
+        <v>0.15</v>
+      </c>
+      <c r="O32" s="2">
         <v>29000</v>
       </c>
-      <c r="J32" s="2">
+      <c r="P32" s="2">
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -1499,31 +2319,55 @@
         <v>30</v>
       </c>
       <c r="C33" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D33" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E33" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F33" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G33" s="2">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H33" s="2">
-        <v>0</v>
-      </c>
-      <c r="I33" s="2">
+        <v>12</v>
+      </c>
+      <c r="I33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="6">
+        <f t="shared" si="4"/>
+        <v>0.375</v>
+      </c>
+      <c r="M33" s="6">
+        <f t="shared" si="5"/>
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="N33" s="6">
+        <f t="shared" si="6"/>
+        <v>0.15</v>
+      </c>
+      <c r="O33" s="2">
         <v>30000</v>
       </c>
-      <c r="J33" s="2">
+      <c r="P33" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -1531,31 +2375,55 @@
         <v>31</v>
       </c>
       <c r="C34" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D34" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E34" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F34" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G34" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H34" s="2">
-        <v>0</v>
-      </c>
-      <c r="I34" s="2">
+        <v>12</v>
+      </c>
+      <c r="I34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="6">
+        <f t="shared" si="4"/>
+        <v>0.35</v>
+      </c>
+      <c r="M34" s="6">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="N34" s="6">
+        <f t="shared" si="6"/>
+        <v>0.15</v>
+      </c>
+      <c r="O34" s="2">
         <v>31000</v>
       </c>
-      <c r="J34" s="2">
+      <c r="P34" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -1563,31 +2431,55 @@
         <v>32</v>
       </c>
       <c r="C35" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D35" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E35" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F35" s="2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G35" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H35" s="2">
-        <v>0</v>
-      </c>
-      <c r="I35" s="2">
+        <v>12</v>
+      </c>
+      <c r="I35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="6">
+        <f t="shared" si="4"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M35" s="6">
+        <f t="shared" si="5"/>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="N35" s="6">
+        <f t="shared" si="6"/>
+        <v>0.15</v>
+      </c>
+      <c r="O35" s="2">
         <v>32000</v>
       </c>
-      <c r="J35" s="2">
+      <c r="P35" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>33</v>
       </c>
@@ -1595,31 +2487,55 @@
         <v>33</v>
       </c>
       <c r="C36" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D36" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E36" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F36" s="2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G36" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H36" s="2">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2">
+        <v>12</v>
+      </c>
+      <c r="I36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="6">
+        <f t="shared" si="4"/>
+        <v>0.3</v>
+      </c>
+      <c r="M36" s="6">
+        <f t="shared" si="5"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="N36" s="6">
+        <f t="shared" si="6"/>
+        <v>0.15</v>
+      </c>
+      <c r="O36" s="2">
         <v>33000</v>
       </c>
-      <c r="J36" s="2">
+      <c r="P36" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>34</v>
       </c>
@@ -1627,31 +2543,55 @@
         <v>34</v>
       </c>
       <c r="C37" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D37" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E37" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F37" s="2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G37" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2">
-        <v>0</v>
-      </c>
-      <c r="I37" s="2">
+        <v>12</v>
+      </c>
+      <c r="I37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="6">
+        <f t="shared" si="4"/>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="M37" s="6">
+        <f t="shared" si="5"/>
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="N37" s="6">
+        <f t="shared" si="6"/>
+        <v>0.15</v>
+      </c>
+      <c r="O37" s="2">
         <v>34000</v>
       </c>
-      <c r="J37" s="2">
+      <c r="P37" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>35</v>
       </c>
@@ -1659,31 +2599,55 @@
         <v>35</v>
       </c>
       <c r="C38" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D38" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E38" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G38" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H38" s="2">
-        <v>0</v>
-      </c>
-      <c r="I38" s="2">
+        <v>12</v>
+      </c>
+      <c r="I38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="6">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="M38" s="6">
+        <f t="shared" si="5"/>
+        <v>0.6</v>
+      </c>
+      <c r="N38" s="6">
+        <f t="shared" si="6"/>
+        <v>0.15</v>
+      </c>
+      <c r="O38" s="2">
         <v>35000</v>
       </c>
-      <c r="J38" s="2">
+      <c r="P38" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>36</v>
       </c>
@@ -1691,27 +2655,51 @@
         <v>36</v>
       </c>
       <c r="C39" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D39" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E39" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F39" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G39" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H39" s="2">
-        <v>0</v>
-      </c>
-      <c r="I39" s="2">
+        <v>12</v>
+      </c>
+      <c r="I39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="6">
+        <f t="shared" si="4"/>
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="M39" s="6">
+        <f t="shared" si="5"/>
+        <v>0.625</v>
+      </c>
+      <c r="N39" s="6">
+        <f t="shared" si="6"/>
+        <v>0.15</v>
+      </c>
+      <c r="O39" s="2">
         <v>36000</v>
       </c>
-      <c r="J39" s="2">
+      <c r="P39" s="2">
         <v>40</v>
       </c>
     </row>

--- a/Assets/Excel/Tree.xlsx
+++ b/Assets/Excel/Tree.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A1AFFF-60FF-423F-BB2A-48BDA701DE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC97BA07-B2A5-4DBA-BD47-33D31264EC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2160" yWindow="1710" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="47">
   <si>
     <t>Int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -149,6 +149,56 @@
   </si>
   <si>
     <t>Rare6Rate</t>
+  </si>
+  <si>
+    <t>String</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落概率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnlockDropItemID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落道具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101;102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101;102;104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropNum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10;5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10;1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10;5;20</t>
+  </si>
+  <si>
+    <t>10;1;15</t>
   </si>
 </sst>
 </file>
@@ -523,19 +573,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="14" width="12.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5" style="2" customWidth="1"/>
+    <col min="17" max="17" width="15.375" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -584,10 +635,17 @@
       <c r="P1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -636,8 +694,17 @@
       <c r="P2" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -686,8 +753,17 @@
       <c r="P3" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -695,13 +771,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -713,37 +789,40 @@
         <v>0</v>
       </c>
       <c r="I4" s="6">
-        <f>C4/SUM($C4:$H4)</f>
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="J4" s="6">
-        <f t="shared" ref="J4:N4" si="0">D4/SUM($C4:$H4)</f>
-        <v>0.1875</v>
+        <v>0.2</v>
       </c>
       <c r="K4" s="6">
-        <f t="shared" si="0"/>
-        <v>6.25E-2</v>
+        <v>0.1</v>
       </c>
       <c r="L4" s="6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M4" s="6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N4" s="6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O4" s="2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="P4" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>101</v>
+      </c>
+      <c r="R4" s="2">
+        <v>10</v>
+      </c>
+      <c r="S4" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -751,13 +830,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="2">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D5" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
@@ -769,37 +848,40 @@
         <v>0</v>
       </c>
       <c r="I5" s="6">
-        <f t="shared" ref="I5:I39" si="1">C5/SUM($C5:$H5)</f>
-        <v>0.72499999999999998</v>
+        <v>0.75</v>
       </c>
       <c r="J5" s="6">
-        <f t="shared" ref="J5:J39" si="2">D5/SUM($C5:$H5)</f>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K5" s="6">
-        <f t="shared" ref="K5:K39" si="3">E5/SUM($C5:$H5)</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L5" s="6">
-        <f t="shared" ref="L5:L39" si="4">F5/SUM($C5:$H5)</f>
         <v>0</v>
       </c>
       <c r="M5" s="6">
-        <f t="shared" ref="M5:M39" si="5">G5/SUM($C5:$H5)</f>
         <v>0</v>
       </c>
       <c r="N5" s="6">
-        <f t="shared" ref="N5:N39" si="6">H5/SUM($C5:$H5)</f>
         <v>0</v>
       </c>
       <c r="O5" s="2">
-        <v>2000</v>
+        <v>110</v>
       </c>
       <c r="P5" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>101</v>
+      </c>
+      <c r="R5" s="2">
+        <v>10</v>
+      </c>
+      <c r="S5" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -807,13 +889,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="2">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D6" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -825,37 +907,40 @@
         <v>0</v>
       </c>
       <c r="I6" s="6">
-        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
       <c r="J6" s="6">
-        <f t="shared" si="2"/>
-        <v>0.21249999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="K6" s="6">
-        <f t="shared" si="3"/>
-        <v>8.7499999999999994E-2</v>
+        <v>0.09</v>
       </c>
       <c r="L6" s="6">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M6" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N6" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O6" s="2">
-        <v>3000</v>
+        <v>120</v>
       </c>
       <c r="P6" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -863,13 +948,13 @@
         <v>4</v>
       </c>
       <c r="C7" s="2">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D7" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -881,37 +966,40 @@
         <v>0</v>
       </c>
       <c r="I7" s="6">
-        <f t="shared" si="1"/>
-        <v>0.67500000000000004</v>
+        <v>0.68</v>
       </c>
       <c r="J7" s="6">
-        <f t="shared" si="2"/>
-        <v>0.22500000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="K7" s="6">
-        <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
       <c r="L7" s="6">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M7" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N7" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O7" s="2">
-        <v>4000</v>
+        <v>130</v>
       </c>
       <c r="P7" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -919,13 +1007,13 @@
         <v>5</v>
       </c>
       <c r="C8" s="2">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D8" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -937,37 +1025,40 @@
         <v>0</v>
       </c>
       <c r="I8" s="6">
-        <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
       <c r="J8" s="6">
-        <f t="shared" si="2"/>
-        <v>0.23749999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="K8" s="6">
-        <f t="shared" si="3"/>
-        <v>0.1125</v>
+        <v>0.11</v>
       </c>
       <c r="L8" s="6">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M8" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N8" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O8" s="2">
-        <v>5000</v>
+        <v>140</v>
       </c>
       <c r="P8" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -975,13 +1066,13 @@
         <v>6</v>
       </c>
       <c r="C9" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E9" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -993,37 +1084,40 @@
         <v>0</v>
       </c>
       <c r="I9" s="6">
-        <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.63</v>
       </c>
       <c r="J9" s="6">
-        <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
       <c r="K9" s="6">
-        <f t="shared" si="3"/>
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="L9" s="6">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M9" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N9" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O9" s="2">
-        <v>6000</v>
+        <v>150</v>
       </c>
       <c r="P9" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1031,13 +1125,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="2">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D10" s="2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E10" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
@@ -1049,37 +1143,40 @@
         <v>0</v>
       </c>
       <c r="I10" s="6">
-        <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
       <c r="J10" s="6">
-        <f t="shared" si="2"/>
-        <v>0.26250000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="K10" s="6">
-        <f t="shared" si="3"/>
-        <v>0.13750000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="L10" s="6">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M10" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N10" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O10" s="2">
-        <v>7000</v>
+        <v>160</v>
       </c>
       <c r="P10" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+        <v>700</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1087,13 +1184,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="2">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D11" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E11" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
@@ -1105,37 +1202,40 @@
         <v>0</v>
       </c>
       <c r="I11" s="6">
-        <f t="shared" si="1"/>
-        <v>0.57499999999999996</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="J11" s="6">
-        <f t="shared" si="2"/>
-        <v>0.27500000000000002</v>
+        <v>0.27</v>
       </c>
       <c r="K11" s="6">
-        <f t="shared" si="3"/>
         <v>0.15</v>
       </c>
       <c r="L11" s="6">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M11" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N11" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O11" s="2">
-        <v>8000</v>
+        <v>170</v>
       </c>
       <c r="P11" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+        <v>800</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -1143,13 +1243,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="2">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D12" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
@@ -1161,37 +1261,40 @@
         <v>0</v>
       </c>
       <c r="I12" s="6">
-        <f t="shared" si="1"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="J12" s="6">
-        <f t="shared" si="2"/>
-        <v>0.28749999999999998</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="K12" s="6">
-        <f t="shared" si="3"/>
-        <v>0.16250000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="L12" s="6">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M12" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N12" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O12" s="2">
-        <v>9000</v>
+        <v>180</v>
       </c>
       <c r="P12" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+        <v>900</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -1199,13 +1302,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="2">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D13" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
@@ -1217,37 +1320,40 @@
         <v>0</v>
       </c>
       <c r="I13" s="6">
-        <f t="shared" si="1"/>
-        <v>0.52500000000000002</v>
+        <v>0.53</v>
       </c>
       <c r="J13" s="6">
-        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="K13" s="6">
-        <f t="shared" si="3"/>
-        <v>0.17499999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="L13" s="6">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M13" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N13" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O13" s="2">
-        <v>10000</v>
+        <v>190</v>
       </c>
       <c r="P13" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -1255,13 +1361,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="2">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D14" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1273,37 +1379,40 @@
         <v>0</v>
       </c>
       <c r="I14" s="6">
-        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="J14" s="6">
-        <f t="shared" si="2"/>
-        <v>0.3125</v>
+        <v>0.31</v>
       </c>
       <c r="K14" s="6">
-        <f t="shared" si="3"/>
-        <v>0.1875</v>
+        <v>0.19</v>
       </c>
       <c r="L14" s="6">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M14" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N14" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O14" s="2">
-        <v>11000</v>
+        <v>200</v>
       </c>
       <c r="P14" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+        <v>1100</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -1311,16 +1420,16 @@
         <v>12</v>
       </c>
       <c r="C15" s="2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F15" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
@@ -1329,37 +1438,40 @@
         <v>0</v>
       </c>
       <c r="I15" s="6">
-        <f t="shared" si="1"/>
-        <v>0.47499999999999998</v>
+        <v>0.48</v>
       </c>
       <c r="J15" s="6">
-        <f t="shared" si="2"/>
-        <v>0.32500000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="K15" s="6">
-        <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
       <c r="L15" s="6">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M15" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N15" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O15" s="2">
-        <v>12000</v>
+        <v>210</v>
       </c>
       <c r="P15" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+        <v>1200</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -1370,13 +1482,13 @@
         <v>0</v>
       </c>
       <c r="D16" s="2">
+        <v>43</v>
+      </c>
+      <c r="E16" s="2">
         <v>36</v>
       </c>
-      <c r="E16" s="2">
-        <v>28</v>
-      </c>
       <c r="F16" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
@@ -1385,37 +1497,40 @@
         <v>0</v>
       </c>
       <c r="I16" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J16" s="6">
-        <f t="shared" si="2"/>
         <v>0.45</v>
       </c>
       <c r="K16" s="6">
-        <f t="shared" si="3"/>
         <v>0.35</v>
       </c>
       <c r="L16" s="6">
-        <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
       <c r="M16" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N16" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O16" s="2">
-        <v>13000</v>
+        <v>220</v>
       </c>
       <c r="P16" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1300</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -1426,13 +1541,13 @@
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E17" s="2">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F17" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
@@ -1441,37 +1556,40 @@
         <v>0</v>
       </c>
       <c r="I17" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J17" s="6">
-        <f t="shared" si="2"/>
-        <v>0.42499999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="K17" s="6">
-        <f t="shared" si="3"/>
-        <v>0.36249999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="L17" s="6">
-        <f t="shared" si="4"/>
-        <v>0.21249999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="M17" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N17" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O17" s="2">
-        <v>14000</v>
+        <v>230</v>
       </c>
       <c r="P17" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1400</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -1482,13 +1600,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="2">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F18" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
@@ -1497,37 +1615,40 @@
         <v>0</v>
       </c>
       <c r="I18" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J18" s="6">
-        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
       <c r="K18" s="6">
-        <f t="shared" si="3"/>
-        <v>0.375</v>
+        <v>0.38</v>
       </c>
       <c r="L18" s="6">
-        <f t="shared" si="4"/>
-        <v>0.22500000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="M18" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N18" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O18" s="2">
-        <v>15000</v>
+        <v>240</v>
       </c>
       <c r="P18" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1500</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -1538,13 +1659,13 @@
         <v>0</v>
       </c>
       <c r="D19" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F19" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
@@ -1553,37 +1674,40 @@
         <v>0</v>
       </c>
       <c r="I19" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J19" s="6">
-        <f t="shared" si="2"/>
-        <v>0.375</v>
+        <v>0.37</v>
       </c>
       <c r="K19" s="6">
-        <f t="shared" si="3"/>
-        <v>0.38750000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="L19" s="6">
-        <f t="shared" si="4"/>
-        <v>0.23749999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="M19" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N19" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O19" s="2">
-        <v>16000</v>
+        <v>250</v>
       </c>
       <c r="P19" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1600</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -1594,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="D20" s="2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F20" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
@@ -1609,37 +1733,40 @@
         <v>0</v>
       </c>
       <c r="I20" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J20" s="6">
-        <f t="shared" si="2"/>
         <v>0.35</v>
       </c>
       <c r="K20" s="6">
-        <f t="shared" si="3"/>
         <v>0.4</v>
       </c>
       <c r="L20" s="6">
-        <f t="shared" si="4"/>
         <v>0.25</v>
       </c>
       <c r="M20" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N20" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O20" s="2">
-        <v>17000</v>
+        <v>260</v>
       </c>
       <c r="P20" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1700</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -1650,13 +1777,13 @@
         <v>0</v>
       </c>
       <c r="D21" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F21" s="2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
@@ -1665,37 +1792,40 @@
         <v>0</v>
       </c>
       <c r="I21" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J21" s="6">
-        <f t="shared" si="2"/>
-        <v>0.32500000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="K21" s="6">
-        <f t="shared" si="3"/>
-        <v>0.41249999999999998</v>
+        <v>0.41</v>
       </c>
       <c r="L21" s="6">
-        <f t="shared" si="4"/>
-        <v>0.26250000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="M21" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N21" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O21" s="2">
-        <v>18000</v>
+        <v>270</v>
       </c>
       <c r="P21" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1800</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -1706,13 +1836,13 @@
         <v>0</v>
       </c>
       <c r="D22" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E22" s="2">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F22" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
@@ -1721,37 +1851,40 @@
         <v>0</v>
       </c>
       <c r="I22" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J22" s="6">
-        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="K22" s="6">
-        <f t="shared" si="3"/>
-        <v>0.42499999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="L22" s="6">
-        <f t="shared" si="4"/>
-        <v>0.27500000000000002</v>
+        <v>0.27</v>
       </c>
       <c r="M22" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N22" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O22" s="2">
-        <v>19000</v>
+        <v>280</v>
       </c>
       <c r="P22" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1900</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -1762,13 +1895,13 @@
         <v>0</v>
       </c>
       <c r="D23" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E23" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F23" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
@@ -1777,37 +1910,40 @@
         <v>0</v>
       </c>
       <c r="I23" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J23" s="6">
-        <f t="shared" si="2"/>
-        <v>0.27500000000000002</v>
+        <v>0.27</v>
       </c>
       <c r="K23" s="6">
-        <f t="shared" si="3"/>
-        <v>0.4375</v>
+        <v>0.44</v>
       </c>
       <c r="L23" s="6">
-        <f t="shared" si="4"/>
-        <v>0.28749999999999998</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M23" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N23" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O23" s="2">
-        <v>20000</v>
+        <v>290</v>
       </c>
       <c r="P23" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2000</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -1818,13 +1954,13 @@
         <v>0</v>
       </c>
       <c r="D24" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E24" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F24" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
@@ -1833,37 +1969,40 @@
         <v>0</v>
       </c>
       <c r="I24" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J24" s="6">
-        <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
       <c r="K24" s="6">
-        <f t="shared" si="3"/>
         <v>0.45</v>
       </c>
       <c r="L24" s="6">
-        <f t="shared" si="4"/>
         <v>0.3</v>
       </c>
       <c r="M24" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N24" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O24" s="2">
-        <v>21000</v>
+        <v>300</v>
       </c>
       <c r="P24" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2100</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -1874,13 +2013,13 @@
         <v>0</v>
       </c>
       <c r="D25" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E25" s="2">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F25" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
@@ -1889,37 +2028,40 @@
         <v>0</v>
       </c>
       <c r="I25" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J25" s="6">
-        <f t="shared" si="2"/>
-        <v>0.22500000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="K25" s="6">
-        <f t="shared" si="3"/>
-        <v>0.46250000000000002</v>
+        <v>0.46</v>
       </c>
       <c r="L25" s="6">
-        <f t="shared" si="4"/>
-        <v>0.3125</v>
+        <v>0.31</v>
       </c>
       <c r="M25" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N25" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O25" s="2">
-        <v>22000</v>
+        <v>310</v>
       </c>
       <c r="P25" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2200</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -1930,13 +2072,13 @@
         <v>0</v>
       </c>
       <c r="D26" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F26" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
@@ -1945,37 +2087,40 @@
         <v>0</v>
       </c>
       <c r="I26" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J26" s="6">
-        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="K26" s="6">
-        <f t="shared" si="3"/>
-        <v>0.47499999999999998</v>
+        <v>0.48</v>
       </c>
       <c r="L26" s="6">
-        <f t="shared" si="4"/>
-        <v>0.32500000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="M26" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N26" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O26" s="2">
-        <v>23000</v>
+        <v>320</v>
       </c>
       <c r="P26" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2300</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -1986,52 +2131,55 @@
         <v>0</v>
       </c>
       <c r="D27" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="G27" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H27" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I27" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J27" s="6">
-        <f t="shared" si="2"/>
-        <v>0.17499999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="K27" s="6">
-        <f t="shared" si="3"/>
-        <v>0.48749999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="L27" s="6">
-        <f t="shared" si="4"/>
-        <v>0.33750000000000002</v>
+        <v>0.34</v>
       </c>
       <c r="M27" s="6">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N27" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O27" s="2">
-        <v>24000</v>
+        <v>330</v>
       </c>
       <c r="P27" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2400</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -2048,46 +2196,49 @@
         <v>0</v>
       </c>
       <c r="F28" s="2">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G28" s="2">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H28" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I28" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J28" s="6">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K28" s="6">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L28" s="6">
-        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="M28" s="6">
-        <f t="shared" si="5"/>
         <v>0.35</v>
       </c>
       <c r="N28" s="6">
-        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="O28" s="2">
-        <v>25000</v>
+        <v>340</v>
       </c>
       <c r="P28" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2500</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -2104,46 +2255,49 @@
         <v>0</v>
       </c>
       <c r="F29" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G29" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H29" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I29" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J29" s="6">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K29" s="6">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L29" s="6">
-        <f t="shared" si="4"/>
-        <v>0.47499999999999998</v>
+        <v>0.48</v>
       </c>
       <c r="M29" s="6">
-        <f t="shared" si="5"/>
-        <v>0.375</v>
+        <v>0.37</v>
       </c>
       <c r="N29" s="6">
-        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="O29" s="2">
-        <v>26000</v>
+        <v>350</v>
       </c>
       <c r="P29" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2600</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -2160,46 +2314,49 @@
         <v>0</v>
       </c>
       <c r="F30" s="2">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G30" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H30" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I30" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J30" s="6">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K30" s="6">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L30" s="6">
-        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="M30" s="6">
-        <f t="shared" si="5"/>
         <v>0.4</v>
       </c>
       <c r="N30" s="6">
-        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="O30" s="2">
-        <v>27000</v>
+        <v>360</v>
       </c>
       <c r="P30" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2700</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -2216,46 +2373,49 @@
         <v>0</v>
       </c>
       <c r="F31" s="2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G31" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="H31" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I31" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J31" s="6">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K31" s="6">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L31" s="6">
-        <f t="shared" si="4"/>
-        <v>0.42499999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="M31" s="6">
-        <f t="shared" si="5"/>
-        <v>0.42499999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="N31" s="6">
-        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="O31" s="2">
-        <v>28000</v>
+        <v>370</v>
       </c>
       <c r="P31" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2800</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -2272,46 +2432,49 @@
         <v>0</v>
       </c>
       <c r="F32" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G32" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="H32" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I32" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J32" s="6">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K32" s="6">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L32" s="6">
-        <f t="shared" si="4"/>
         <v>0.4</v>
       </c>
       <c r="M32" s="6">
-        <f t="shared" si="5"/>
         <v>0.45</v>
       </c>
       <c r="N32" s="6">
-        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="O32" s="2">
-        <v>29000</v>
+        <v>380</v>
       </c>
       <c r="P32" s="2">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2900</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -2328,46 +2491,49 @@
         <v>0</v>
       </c>
       <c r="F33" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G33" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H33" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I33" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J33" s="6">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K33" s="6">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L33" s="6">
-        <f t="shared" si="4"/>
-        <v>0.375</v>
+        <v>0.38</v>
       </c>
       <c r="M33" s="6">
-        <f t="shared" si="5"/>
-        <v>0.47499999999999998</v>
+        <v>0.47</v>
       </c>
       <c r="N33" s="6">
-        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="O33" s="2">
-        <v>30000</v>
+        <v>390</v>
       </c>
       <c r="P33" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+        <v>3000</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -2384,46 +2550,49 @@
         <v>0</v>
       </c>
       <c r="F34" s="2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G34" s="2">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H34" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I34" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J34" s="6">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K34" s="6">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L34" s="6">
-        <f t="shared" si="4"/>
         <v>0.35</v>
       </c>
       <c r="M34" s="6">
-        <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
       <c r="N34" s="6">
-        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="O34" s="2">
-        <v>31000</v>
+        <v>400</v>
       </c>
       <c r="P34" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+        <v>3100</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -2440,46 +2609,49 @@
         <v>0</v>
       </c>
       <c r="F35" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G35" s="2">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H35" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J35" s="6">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K35" s="6">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L35" s="6">
-        <f t="shared" si="4"/>
-        <v>0.32500000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="M35" s="6">
-        <f t="shared" si="5"/>
-        <v>0.52500000000000002</v>
+        <v>0.52</v>
       </c>
       <c r="N35" s="6">
-        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="O35" s="2">
-        <v>32000</v>
+        <v>410</v>
       </c>
       <c r="P35" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+        <v>3200</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>33</v>
       </c>
@@ -2496,46 +2668,49 @@
         <v>0</v>
       </c>
       <c r="F36" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G36" s="2">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H36" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I36" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J36" s="6">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K36" s="6">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L36" s="6">
-        <f t="shared" si="4"/>
         <v>0.3</v>
       </c>
       <c r="M36" s="6">
-        <f t="shared" si="5"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="N36" s="6">
-        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="O36" s="2">
-        <v>33000</v>
+        <v>420</v>
       </c>
       <c r="P36" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+        <v>3300</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>34</v>
       </c>
@@ -2552,46 +2727,49 @@
         <v>0</v>
       </c>
       <c r="F37" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G37" s="2">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H37" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I37" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J37" s="6">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K37" s="6">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L37" s="6">
-        <f t="shared" si="4"/>
-        <v>0.27500000000000002</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M37" s="6">
-        <f t="shared" si="5"/>
-        <v>0.57499999999999996</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="N37" s="6">
-        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="O37" s="2">
-        <v>34000</v>
+        <v>430</v>
       </c>
       <c r="P37" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+        <v>3400</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>35</v>
       </c>
@@ -2608,46 +2786,49 @@
         <v>0</v>
       </c>
       <c r="F38" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G38" s="2">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H38" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I38" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J38" s="6">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K38" s="6">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L38" s="6">
-        <f t="shared" si="4"/>
         <v>0.25</v>
       </c>
       <c r="M38" s="6">
-        <f t="shared" si="5"/>
         <v>0.6</v>
       </c>
       <c r="N38" s="6">
-        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="O38" s="2">
-        <v>35000</v>
+        <v>440</v>
       </c>
       <c r="P38" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+        <v>3500</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>36</v>
       </c>
@@ -2664,43 +2845,46 @@
         <v>0</v>
       </c>
       <c r="F39" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G39" s="2">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H39" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I39" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J39" s="6">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K39" s="6">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L39" s="6">
-        <f t="shared" si="4"/>
-        <v>0.22500000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="M39" s="6">
-        <f t="shared" si="5"/>
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="N39" s="6">
-        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="O39" s="2">
-        <v>36000</v>
+        <v>450</v>
       </c>
       <c r="P39" s="2">
-        <v>40</v>
+        <v>3600</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
